--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/04 Abril/Liquidacióncvs - ensayo/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1690" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D32CCE26-9358-4BEE-B020-73D15C77B158}"/>
+  <xr:revisionPtr revIDLastSave="1717" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D12EB7FD-183E-4DCD-BEC8-A71DAB118F36}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -38316,7 +38316,7 @@
         <v>86</v>
       </c>
       <c r="G1447">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="H1447"/>
     </row>
@@ -38331,7 +38331,7 @@
         <v>86</v>
       </c>
       <c r="G1448">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="H1448"/>
     </row>
@@ -38361,7 +38361,7 @@
         <v>86</v>
       </c>
       <c r="G1450">
-        <v>1</v>
+        <v>202</v>
       </c>
       <c r="H1450"/>
     </row>
@@ -38376,7 +38376,7 @@
         <v>86</v>
       </c>
       <c r="G1451">
-        <v>1</v>
+        <v>294</v>
       </c>
       <c r="H1451"/>
     </row>
@@ -38391,7 +38391,7 @@
         <v>86</v>
       </c>
       <c r="G1452">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="H1452"/>
     </row>
@@ -38406,7 +38406,7 @@
         <v>86</v>
       </c>
       <c r="G1453">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="H1453"/>
     </row>
@@ -38421,7 +38421,7 @@
         <v>86</v>
       </c>
       <c r="G1454">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H1454"/>
     </row>
@@ -38436,7 +38436,7 @@
         <v>86</v>
       </c>
       <c r="G1455">
-        <v>1</v>
+        <v>156</v>
       </c>
       <c r="H1455"/>
     </row>
@@ -38451,7 +38451,7 @@
         <v>86</v>
       </c>
       <c r="G1456">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="H1456"/>
     </row>
@@ -38466,7 +38466,7 @@
         <v>86</v>
       </c>
       <c r="G1457">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H1457"/>
     </row>
@@ -38481,7 +38481,7 @@
         <v>86</v>
       </c>
       <c r="G1458">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="H1458"/>
     </row>
@@ -38496,7 +38496,7 @@
         <v>86</v>
       </c>
       <c r="G1459">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="H1459"/>
     </row>
@@ -38511,7 +38511,7 @@
         <v>86</v>
       </c>
       <c r="G1460">
-        <v>1</v>
+        <v>247</v>
       </c>
       <c r="H1460"/>
     </row>
@@ -38526,7 +38526,7 @@
         <v>86</v>
       </c>
       <c r="G1461">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="H1461"/>
     </row>
@@ -38541,7 +38541,7 @@
         <v>86</v>
       </c>
       <c r="G1462">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="H1462"/>
     </row>
@@ -38556,7 +38556,7 @@
         <v>86</v>
       </c>
       <c r="G1463">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="H1463"/>
     </row>
@@ -38571,7 +38571,7 @@
         <v>86</v>
       </c>
       <c r="G1464">
-        <v>1</v>
+        <v>288</v>
       </c>
       <c r="H1464"/>
     </row>
@@ -38586,7 +38586,7 @@
         <v>86</v>
       </c>
       <c r="G1465">
-        <v>1</v>
+        <v>260</v>
       </c>
       <c r="H1465"/>
     </row>
@@ -38601,7 +38601,7 @@
         <v>86</v>
       </c>
       <c r="G1466">
-        <v>1</v>
+        <v>233</v>
       </c>
       <c r="H1466"/>
     </row>
@@ -38616,7 +38616,7 @@
         <v>86</v>
       </c>
       <c r="G1467">
-        <v>1</v>
+        <v>314</v>
       </c>
       <c r="H1467"/>
     </row>
@@ -38631,7 +38631,7 @@
         <v>86</v>
       </c>
       <c r="G1468">
-        <v>1</v>
+        <v>381</v>
       </c>
       <c r="H1468"/>
     </row>
@@ -38646,7 +38646,7 @@
         <v>86</v>
       </c>
       <c r="G1469">
-        <v>1</v>
+        <v>4841</v>
       </c>
       <c r="H1469"/>
     </row>
